--- a/Prueba.xlsx
+++ b/Prueba.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ARGUM\Downloads\ADSO PROYECTOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ARGUM\Downloads\ADSO PROYECTOS\Gt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19459E19-B089-46E9-AA91-C6ED0D3E5879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{482302E4-5ABD-4034-B46C-016D97C55B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{4FBC206D-03E5-4E8D-AD12-6BBB13D0EDCB}"/>
   </bookViews>
@@ -34,6 +34,14 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>Prueba1</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -385,7 +393,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9B7609B-BBD9-451F-AAA3-074688303BE5}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>